--- a/resultados/xambre/erros_varredura.xlsx
+++ b/resultados/xambre/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F450"/>
+  <dimension ref="A1:F594"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13020,6 +13020,4038 @@
         </is>
       </c>
     </row>
+    <row r="451">
+      <c r="A451" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B451" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=748</t>
+        </is>
+      </c>
+      <c r="C451" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D451" t="n">
+        <v>500</v>
+      </c>
+      <c r="E451" t="n">
+        <v>3</v>
+      </c>
+      <c r="F451" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:13:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="452">
+      <c r="A452" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B452" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=748</t>
+        </is>
+      </c>
+      <c r="C452" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D452" t="n">
+        <v>0</v>
+      </c>
+      <c r="E452" t="n">
+        <v>3</v>
+      </c>
+      <c r="F452" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:14:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="453">
+      <c r="A453" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B453" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=744</t>
+        </is>
+      </c>
+      <c r="C453" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D453" t="n">
+        <v>500</v>
+      </c>
+      <c r="E453" t="n">
+        <v>3</v>
+      </c>
+      <c r="F453" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:14:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="454">
+      <c r="A454" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B454" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=744</t>
+        </is>
+      </c>
+      <c r="C454" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D454" t="n">
+        <v>0</v>
+      </c>
+      <c r="E454" t="n">
+        <v>3</v>
+      </c>
+      <c r="F454" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:15:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="455">
+      <c r="A455" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B455" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=718</t>
+        </is>
+      </c>
+      <c r="C455" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D455" t="n">
+        <v>500</v>
+      </c>
+      <c r="E455" t="n">
+        <v>3</v>
+      </c>
+      <c r="F455" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:16:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="456">
+      <c r="A456" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B456" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=718</t>
+        </is>
+      </c>
+      <c r="C456" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D456" t="n">
+        <v>0</v>
+      </c>
+      <c r="E456" t="n">
+        <v>3</v>
+      </c>
+      <c r="F456" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:17:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="457">
+      <c r="A457" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B457" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=559</t>
+        </is>
+      </c>
+      <c r="C457" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D457" t="n">
+        <v>500</v>
+      </c>
+      <c r="E457" t="n">
+        <v>3</v>
+      </c>
+      <c r="F457" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:17:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="458">
+      <c r="A458" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B458" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=559</t>
+        </is>
+      </c>
+      <c r="C458" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D458" t="n">
+        <v>0</v>
+      </c>
+      <c r="E458" t="n">
+        <v>3</v>
+      </c>
+      <c r="F458" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:18:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="459">
+      <c r="A459" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B459" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=151</t>
+        </is>
+      </c>
+      <c r="C459" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D459" t="n">
+        <v>500</v>
+      </c>
+      <c r="E459" t="n">
+        <v>3</v>
+      </c>
+      <c r="F459" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:18:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="460">
+      <c r="A460" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B460" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=151</t>
+        </is>
+      </c>
+      <c r="C460" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D460" t="n">
+        <v>0</v>
+      </c>
+      <c r="E460" t="n">
+        <v>3</v>
+      </c>
+      <c r="F460" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:19:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="461">
+      <c r="A461" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B461" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=150</t>
+        </is>
+      </c>
+      <c r="C461" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D461" t="n">
+        <v>500</v>
+      </c>
+      <c r="E461" t="n">
+        <v>3</v>
+      </c>
+      <c r="F461" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:20:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="462">
+      <c r="A462" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B462" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=150</t>
+        </is>
+      </c>
+      <c r="C462" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D462" t="n">
+        <v>0</v>
+      </c>
+      <c r="E462" t="n">
+        <v>3</v>
+      </c>
+      <c r="F462" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:21:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="463">
+      <c r="A463" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B463" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=149</t>
+        </is>
+      </c>
+      <c r="C463" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D463" t="n">
+        <v>500</v>
+      </c>
+      <c r="E463" t="n">
+        <v>3</v>
+      </c>
+      <c r="F463" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:21:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="464">
+      <c r="A464" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B464" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=149</t>
+        </is>
+      </c>
+      <c r="C464" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D464" t="n">
+        <v>0</v>
+      </c>
+      <c r="E464" t="n">
+        <v>3</v>
+      </c>
+      <c r="F464" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:22:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="465">
+      <c r="A465" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B465" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=148</t>
+        </is>
+      </c>
+      <c r="C465" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D465" t="n">
+        <v>500</v>
+      </c>
+      <c r="E465" t="n">
+        <v>3</v>
+      </c>
+      <c r="F465" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:22:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="466">
+      <c r="A466" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B466" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=148</t>
+        </is>
+      </c>
+      <c r="C466" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D466" t="n">
+        <v>0</v>
+      </c>
+      <c r="E466" t="n">
+        <v>3</v>
+      </c>
+      <c r="F466" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:23:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="467">
+      <c r="A467" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B467" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=147</t>
+        </is>
+      </c>
+      <c r="C467" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D467" t="n">
+        <v>500</v>
+      </c>
+      <c r="E467" t="n">
+        <v>3</v>
+      </c>
+      <c r="F467" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:24:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="468">
+      <c r="A468" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B468" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=147</t>
+        </is>
+      </c>
+      <c r="C468" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D468" t="n">
+        <v>0</v>
+      </c>
+      <c r="E468" t="n">
+        <v>3</v>
+      </c>
+      <c r="F468" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:25:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="469">
+      <c r="A469" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B469" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=146</t>
+        </is>
+      </c>
+      <c r="C469" t="inlineStr">
+        <is>
+          <t>HTTP_500</t>
+        </is>
+      </c>
+      <c r="D469" t="n">
+        <v>500</v>
+      </c>
+      <c r="E469" t="n">
+        <v>3</v>
+      </c>
+      <c r="F469" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:25:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="470">
+      <c r="A470" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B470" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/licitacao/impressao?id=146</t>
+        </is>
+      </c>
+      <c r="C470" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D470" t="n">
+        <v>0</v>
+      </c>
+      <c r="E470" t="n">
+        <v>3</v>
+      </c>
+      <c r="F470" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:26:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="471">
+      <c r="A471" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B471" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/145/dispensa-de-licitacao-n-0102023</t>
+        </is>
+      </c>
+      <c r="C471" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D471" t="n">
+        <v>404</v>
+      </c>
+      <c r="E471" t="n">
+        <v>3</v>
+      </c>
+      <c r="F471" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:26:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="472">
+      <c r="A472" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B472" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/145/dispensa-de-licitacao-n-0102023</t>
+        </is>
+      </c>
+      <c r="C472" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D472" t="n">
+        <v>0</v>
+      </c>
+      <c r="E472" t="n">
+        <v>3</v>
+      </c>
+      <c r="F472" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:27:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="473">
+      <c r="A473" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B473" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/143/dispensa-de-licitacao-n-0062023</t>
+        </is>
+      </c>
+      <c r="C473" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D473" t="n">
+        <v>404</v>
+      </c>
+      <c r="E473" t="n">
+        <v>3</v>
+      </c>
+      <c r="F473" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:27:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="474">
+      <c r="A474" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B474" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/143/dispensa-de-licitacao-n-0062023</t>
+        </is>
+      </c>
+      <c r="C474" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D474" t="n">
+        <v>0</v>
+      </c>
+      <c r="E474" t="n">
+        <v>3</v>
+      </c>
+      <c r="F474" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:29:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="475">
+      <c r="A475" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B475" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/144/dispensa-de-licitacao-n-0082023</t>
+        </is>
+      </c>
+      <c r="C475" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D475" t="n">
+        <v>404</v>
+      </c>
+      <c r="E475" t="n">
+        <v>3</v>
+      </c>
+      <c r="F475" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:29:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="476">
+      <c r="A476" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B476" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/144/dispensa-de-licitacao-n-0082023</t>
+        </is>
+      </c>
+      <c r="C476" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D476" t="n">
+        <v>0</v>
+      </c>
+      <c r="E476" t="n">
+        <v>3</v>
+      </c>
+      <c r="F476" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:30:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="477">
+      <c r="A477" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B477" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/142/dispensa-de-licitacao-n-0072023</t>
+        </is>
+      </c>
+      <c r="C477" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D477" t="n">
+        <v>404</v>
+      </c>
+      <c r="E477" t="n">
+        <v>3</v>
+      </c>
+      <c r="F477" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:30:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="478">
+      <c r="A478" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B478" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/142/dispensa-de-licitacao-n-0072023</t>
+        </is>
+      </c>
+      <c r="C478" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D478" t="n">
+        <v>0</v>
+      </c>
+      <c r="E478" t="n">
+        <v>3</v>
+      </c>
+      <c r="F478" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:31:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="479">
+      <c r="A479" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B479" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/141/dispensa-de-licitacao-n-0032023</t>
+        </is>
+      </c>
+      <c r="C479" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D479" t="n">
+        <v>404</v>
+      </c>
+      <c r="E479" t="n">
+        <v>3</v>
+      </c>
+      <c r="F479" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:31:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="480">
+      <c r="A480" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B480" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/141/dispensa-de-licitacao-n-0032023</t>
+        </is>
+      </c>
+      <c r="C480" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D480" t="n">
+        <v>0</v>
+      </c>
+      <c r="E480" t="n">
+        <v>3</v>
+      </c>
+      <c r="F480" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:32:43</t>
+        </is>
+      </c>
+    </row>
+    <row r="481">
+      <c r="A481" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B481" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/140/dispensa-de-licitacao-n-0042023</t>
+        </is>
+      </c>
+      <c r="C481" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D481" t="n">
+        <v>404</v>
+      </c>
+      <c r="E481" t="n">
+        <v>3</v>
+      </c>
+      <c r="F481" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:32:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="482">
+      <c r="A482" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B482" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/140/dispensa-de-licitacao-n-0042023</t>
+        </is>
+      </c>
+      <c r="C482" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D482" t="n">
+        <v>0</v>
+      </c>
+      <c r="E482" t="n">
+        <v>3</v>
+      </c>
+      <c r="F482" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:33:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="483">
+      <c r="A483" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B483" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/139/dispensa-de-licitacao-n-0022023</t>
+        </is>
+      </c>
+      <c r="C483" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D483" t="n">
+        <v>404</v>
+      </c>
+      <c r="E483" t="n">
+        <v>3</v>
+      </c>
+      <c r="F483" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:33:55</t>
+        </is>
+      </c>
+    </row>
+    <row r="484">
+      <c r="A484" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B484" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/139/dispensa-de-licitacao-n-0022023</t>
+        </is>
+      </c>
+      <c r="C484" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D484" t="n">
+        <v>0</v>
+      </c>
+      <c r="E484" t="n">
+        <v>3</v>
+      </c>
+      <c r="F484" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:35:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="485">
+      <c r="A485" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B485" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/137/dispensa-de-licitacao-n-0142022</t>
+        </is>
+      </c>
+      <c r="C485" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D485" t="n">
+        <v>404</v>
+      </c>
+      <c r="E485" t="n">
+        <v>3</v>
+      </c>
+      <c r="F485" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:35:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="486">
+      <c r="A486" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B486" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/137/dispensa-de-licitacao-n-0142022</t>
+        </is>
+      </c>
+      <c r="C486" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D486" t="n">
+        <v>0</v>
+      </c>
+      <c r="E486" t="n">
+        <v>3</v>
+      </c>
+      <c r="F486" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:36:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="487">
+      <c r="A487" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B487" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/136/dispensa-de-licitacao-n-0132022</t>
+        </is>
+      </c>
+      <c r="C487" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D487" t="n">
+        <v>404</v>
+      </c>
+      <c r="E487" t="n">
+        <v>3</v>
+      </c>
+      <c r="F487" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:36:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="488">
+      <c r="A488" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B488" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/136/dispensa-de-licitacao-n-0132022</t>
+        </is>
+      </c>
+      <c r="C488" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D488" t="n">
+        <v>0</v>
+      </c>
+      <c r="E488" t="n">
+        <v>3</v>
+      </c>
+      <c r="F488" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:37:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="489">
+      <c r="A489" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B489" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/138/dispensa-de-licitacao-n-0012023</t>
+        </is>
+      </c>
+      <c r="C489" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D489" t="n">
+        <v>404</v>
+      </c>
+      <c r="E489" t="n">
+        <v>3</v>
+      </c>
+      <c r="F489" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:37:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="490">
+      <c r="A490" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B490" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/138/dispensa-de-licitacao-n-0012023</t>
+        </is>
+      </c>
+      <c r="C490" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D490" t="n">
+        <v>0</v>
+      </c>
+      <c r="E490" t="n">
+        <v>3</v>
+      </c>
+      <c r="F490" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:38:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="491">
+      <c r="A491" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B491" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/135/dispensa-de-licitacao-n-0122022</t>
+        </is>
+      </c>
+      <c r="C491" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D491" t="n">
+        <v>404</v>
+      </c>
+      <c r="E491" t="n">
+        <v>3</v>
+      </c>
+      <c r="F491" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:38:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="492">
+      <c r="A492" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B492" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/135/dispensa-de-licitacao-n-0122022</t>
+        </is>
+      </c>
+      <c r="C492" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D492" t="n">
+        <v>0</v>
+      </c>
+      <c r="E492" t="n">
+        <v>3</v>
+      </c>
+      <c r="F492" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:39:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="493">
+      <c r="A493" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B493" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/133/dispensa-de-licitacao-n-0102022</t>
+        </is>
+      </c>
+      <c r="C493" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D493" t="n">
+        <v>404</v>
+      </c>
+      <c r="E493" t="n">
+        <v>3</v>
+      </c>
+      <c r="F493" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:39:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="494">
+      <c r="A494" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B494" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/133/dispensa-de-licitacao-n-0102022</t>
+        </is>
+      </c>
+      <c r="C494" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D494" t="n">
+        <v>0</v>
+      </c>
+      <c r="E494" t="n">
+        <v>3</v>
+      </c>
+      <c r="F494" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:41:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="495">
+      <c r="A495" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B495" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/134/dispensa-de-licitacao-n-0112022</t>
+        </is>
+      </c>
+      <c r="C495" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D495" t="n">
+        <v>404</v>
+      </c>
+      <c r="E495" t="n">
+        <v>3</v>
+      </c>
+      <c r="F495" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:41:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="496">
+      <c r="A496" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B496" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/134/dispensa-de-licitacao-n-0112022</t>
+        </is>
+      </c>
+      <c r="C496" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D496" t="n">
+        <v>0</v>
+      </c>
+      <c r="E496" t="n">
+        <v>3</v>
+      </c>
+      <c r="F496" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:42:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="497">
+      <c r="A497" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B497" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/132/dispensa-de-licitacao-n-0092022</t>
+        </is>
+      </c>
+      <c r="C497" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D497" t="n">
+        <v>404</v>
+      </c>
+      <c r="E497" t="n">
+        <v>3</v>
+      </c>
+      <c r="F497" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:42:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="498">
+      <c r="A498" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B498" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/132/dispensa-de-licitacao-n-0092022</t>
+        </is>
+      </c>
+      <c r="C498" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D498" t="n">
+        <v>0</v>
+      </c>
+      <c r="E498" t="n">
+        <v>3</v>
+      </c>
+      <c r="F498" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:43:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="499">
+      <c r="A499" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B499" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/131/dispensa-de-licitacao-n-0082022</t>
+        </is>
+      </c>
+      <c r="C499" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D499" t="n">
+        <v>404</v>
+      </c>
+      <c r="E499" t="n">
+        <v>3</v>
+      </c>
+      <c r="F499" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:43:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="500">
+      <c r="A500" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B500" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/131/dispensa-de-licitacao-n-0082022</t>
+        </is>
+      </c>
+      <c r="C500" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D500" t="n">
+        <v>0</v>
+      </c>
+      <c r="E500" t="n">
+        <v>3</v>
+      </c>
+      <c r="F500" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:44:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="501">
+      <c r="A501" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B501" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/130/dispensa-de-licitacao-n-0072022</t>
+        </is>
+      </c>
+      <c r="C501" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D501" t="n">
+        <v>404</v>
+      </c>
+      <c r="E501" t="n">
+        <v>3</v>
+      </c>
+      <c r="F501" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:44:40</t>
+        </is>
+      </c>
+    </row>
+    <row r="502">
+      <c r="A502" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B502" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/130/dispensa-de-licitacao-n-0072022</t>
+        </is>
+      </c>
+      <c r="C502" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D502" t="n">
+        <v>0</v>
+      </c>
+      <c r="E502" t="n">
+        <v>3</v>
+      </c>
+      <c r="F502" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:45:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="503">
+      <c r="A503" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B503" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/85/dispensa-de-licitacao-n-0032022</t>
+        </is>
+      </c>
+      <c r="C503" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D503" t="n">
+        <v>404</v>
+      </c>
+      <c r="E503" t="n">
+        <v>3</v>
+      </c>
+      <c r="F503" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:45:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="504">
+      <c r="A504" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B504" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/85/dispensa-de-licitacao-n-0032022</t>
+        </is>
+      </c>
+      <c r="C504" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D504" t="n">
+        <v>0</v>
+      </c>
+      <c r="E504" t="n">
+        <v>3</v>
+      </c>
+      <c r="F504" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:47:02</t>
+        </is>
+      </c>
+    </row>
+    <row r="505">
+      <c r="A505" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B505" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/127/dispensa-de-licitacao-n-0062022</t>
+        </is>
+      </c>
+      <c r="C505" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D505" t="n">
+        <v>404</v>
+      </c>
+      <c r="E505" t="n">
+        <v>3</v>
+      </c>
+      <c r="F505" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:47:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="506">
+      <c r="A506" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B506" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/127/dispensa-de-licitacao-n-0062022</t>
+        </is>
+      </c>
+      <c r="C506" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D506" t="n">
+        <v>0</v>
+      </c>
+      <c r="E506" t="n">
+        <v>3</v>
+      </c>
+      <c r="F506" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:48:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="507">
+      <c r="A507" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B507" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/129/dispensa-de-licitacao-n-0042022</t>
+        </is>
+      </c>
+      <c r="C507" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D507" t="n">
+        <v>404</v>
+      </c>
+      <c r="E507" t="n">
+        <v>3</v>
+      </c>
+      <c r="F507" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:48:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B508" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/129/dispensa-de-licitacao-n-0042022</t>
+        </is>
+      </c>
+      <c r="C508" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D508" t="n">
+        <v>0</v>
+      </c>
+      <c r="E508" t="n">
+        <v>3</v>
+      </c>
+      <c r="F508" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:49:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B509" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/128/dispensa-de-licitacao-n-0032022-2</t>
+        </is>
+      </c>
+      <c r="C509" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D509" t="n">
+        <v>404</v>
+      </c>
+      <c r="E509" t="n">
+        <v>3</v>
+      </c>
+      <c r="F509" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:49:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B510" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/128/dispensa-de-licitacao-n-0032022-2</t>
+        </is>
+      </c>
+      <c r="C510" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D510" t="n">
+        <v>0</v>
+      </c>
+      <c r="E510" t="n">
+        <v>3</v>
+      </c>
+      <c r="F510" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:50:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B511" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/126/dispensa-de-licitacao-n-0022022</t>
+        </is>
+      </c>
+      <c r="C511" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D511" t="n">
+        <v>404</v>
+      </c>
+      <c r="E511" t="n">
+        <v>3</v>
+      </c>
+      <c r="F511" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:50:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B512" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/126/dispensa-de-licitacao-n-0022022</t>
+        </is>
+      </c>
+      <c r="C512" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D512" t="n">
+        <v>0</v>
+      </c>
+      <c r="E512" t="n">
+        <v>3</v>
+      </c>
+      <c r="F512" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:51:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B513" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/125/dispensa-de-licitacao-n-0012022</t>
+        </is>
+      </c>
+      <c r="C513" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D513" t="n">
+        <v>404</v>
+      </c>
+      <c r="E513" t="n">
+        <v>3</v>
+      </c>
+      <c r="F513" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:51:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B514" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/125/dispensa-de-licitacao-n-0012022</t>
+        </is>
+      </c>
+      <c r="C514" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D514" t="n">
+        <v>0</v>
+      </c>
+      <c r="E514" t="n">
+        <v>3</v>
+      </c>
+      <c r="F514" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:53:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B515" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/124/dispensa-de-licitacao-n-0122021</t>
+        </is>
+      </c>
+      <c r="C515" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D515" t="n">
+        <v>404</v>
+      </c>
+      <c r="E515" t="n">
+        <v>3</v>
+      </c>
+      <c r="F515" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:53:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B516" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/124/dispensa-de-licitacao-n-0122021</t>
+        </is>
+      </c>
+      <c r="C516" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D516" t="n">
+        <v>0</v>
+      </c>
+      <c r="E516" t="n">
+        <v>3</v>
+      </c>
+      <c r="F516" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:54:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B517" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/123/dispensa-de-licitacao-n-0112021</t>
+        </is>
+      </c>
+      <c r="C517" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D517" t="n">
+        <v>404</v>
+      </c>
+      <c r="E517" t="n">
+        <v>3</v>
+      </c>
+      <c r="F517" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:54:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B518" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/123/dispensa-de-licitacao-n-0112021</t>
+        </is>
+      </c>
+      <c r="C518" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D518" t="n">
+        <v>0</v>
+      </c>
+      <c r="E518" t="n">
+        <v>3</v>
+      </c>
+      <c r="F518" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:55:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B519" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/122/dispensa-de-licitacao-n-0102021</t>
+        </is>
+      </c>
+      <c r="C519" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D519" t="n">
+        <v>404</v>
+      </c>
+      <c r="E519" t="n">
+        <v>3</v>
+      </c>
+      <c r="F519" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:55:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B520" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/122/dispensa-de-licitacao-n-0102021</t>
+        </is>
+      </c>
+      <c r="C520" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D520" t="n">
+        <v>0</v>
+      </c>
+      <c r="E520" t="n">
+        <v>3</v>
+      </c>
+      <c r="F520" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:56:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B521" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/121/dispensa-de-licitacao-n-0092021</t>
+        </is>
+      </c>
+      <c r="C521" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D521" t="n">
+        <v>404</v>
+      </c>
+      <c r="E521" t="n">
+        <v>3</v>
+      </c>
+      <c r="F521" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:56:39</t>
+        </is>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B522" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/121/dispensa-de-licitacao-n-0092021</t>
+        </is>
+      </c>
+      <c r="C522" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D522" t="n">
+        <v>0</v>
+      </c>
+      <c r="E522" t="n">
+        <v>3</v>
+      </c>
+      <c r="F522" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:57:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B523" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/120/dispensa-de-licitacao-n-0082021</t>
+        </is>
+      </c>
+      <c r="C523" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D523" t="n">
+        <v>404</v>
+      </c>
+      <c r="E523" t="n">
+        <v>3</v>
+      </c>
+      <c r="F523" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:57:51</t>
+        </is>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B524" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/120/dispensa-de-licitacao-n-0082021</t>
+        </is>
+      </c>
+      <c r="C524" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D524" t="n">
+        <v>0</v>
+      </c>
+      <c r="E524" t="n">
+        <v>3</v>
+      </c>
+      <c r="F524" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:59:01</t>
+        </is>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B525" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/119/dispensa-de-licitacao-n-0072021</t>
+        </is>
+      </c>
+      <c r="C525" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D525" t="n">
+        <v>404</v>
+      </c>
+      <c r="E525" t="n">
+        <v>3</v>
+      </c>
+      <c r="F525" t="inlineStr">
+        <is>
+          <t>2026-07-31 20:59:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B526" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/119/dispensa-de-licitacao-n-0072021</t>
+        </is>
+      </c>
+      <c r="C526" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D526" t="n">
+        <v>0</v>
+      </c>
+      <c r="E526" t="n">
+        <v>3</v>
+      </c>
+      <c r="F526" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:00:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B527" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/118/dispensa-de-licitacao-n-0062021</t>
+        </is>
+      </c>
+      <c r="C527" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D527" t="n">
+        <v>404</v>
+      </c>
+      <c r="E527" t="n">
+        <v>3</v>
+      </c>
+      <c r="F527" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:00:15</t>
+        </is>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B528" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/118/dispensa-de-licitacao-n-0062021</t>
+        </is>
+      </c>
+      <c r="C528" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D528" t="n">
+        <v>0</v>
+      </c>
+      <c r="E528" t="n">
+        <v>3</v>
+      </c>
+      <c r="F528" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:01:25</t>
+        </is>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B529" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/117/dispensa-de-licitacao-n-0052021</t>
+        </is>
+      </c>
+      <c r="C529" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D529" t="n">
+        <v>404</v>
+      </c>
+      <c r="E529" t="n">
+        <v>3</v>
+      </c>
+      <c r="F529" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:01:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B530" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/117/dispensa-de-licitacao-n-0052021</t>
+        </is>
+      </c>
+      <c r="C530" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D530" t="n">
+        <v>0</v>
+      </c>
+      <c r="E530" t="n">
+        <v>3</v>
+      </c>
+      <c r="F530" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:02:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B531" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/116/dispensa-de-licitacao-n-0042021</t>
+        </is>
+      </c>
+      <c r="C531" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D531" t="n">
+        <v>404</v>
+      </c>
+      <c r="E531" t="n">
+        <v>3</v>
+      </c>
+      <c r="F531" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:02:38</t>
+        </is>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B532" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/116/dispensa-de-licitacao-n-0042021</t>
+        </is>
+      </c>
+      <c r="C532" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D532" t="n">
+        <v>0</v>
+      </c>
+      <c r="E532" t="n">
+        <v>3</v>
+      </c>
+      <c r="F532" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:03:48</t>
+        </is>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B533" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/115/dispensa-de-licitacao-n-0032021</t>
+        </is>
+      </c>
+      <c r="C533" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D533" t="n">
+        <v>404</v>
+      </c>
+      <c r="E533" t="n">
+        <v>3</v>
+      </c>
+      <c r="F533" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:03:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B534" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/115/dispensa-de-licitacao-n-0032021</t>
+        </is>
+      </c>
+      <c r="C534" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D534" t="n">
+        <v>0</v>
+      </c>
+      <c r="E534" t="n">
+        <v>3</v>
+      </c>
+      <c r="F534" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:04:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B535" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/114/dispensa-de-licitacao-n-0022021</t>
+        </is>
+      </c>
+      <c r="C535" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D535" t="n">
+        <v>404</v>
+      </c>
+      <c r="E535" t="n">
+        <v>3</v>
+      </c>
+      <c r="F535" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:05:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B536" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/114/dispensa-de-licitacao-n-0022021</t>
+        </is>
+      </c>
+      <c r="C536" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D536" t="n">
+        <v>0</v>
+      </c>
+      <c r="E536" t="n">
+        <v>3</v>
+      </c>
+      <c r="F536" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:06:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B537" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/113/dispensa-de-licitacao-n-0012021</t>
+        </is>
+      </c>
+      <c r="C537" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D537" t="n">
+        <v>404</v>
+      </c>
+      <c r="E537" t="n">
+        <v>3</v>
+      </c>
+      <c r="F537" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:06:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="538">
+      <c r="A538" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B538" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/113/dispensa-de-licitacao-n-0012021</t>
+        </is>
+      </c>
+      <c r="C538" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D538" t="n">
+        <v>0</v>
+      </c>
+      <c r="E538" t="n">
+        <v>3</v>
+      </c>
+      <c r="F538" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:07:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="539">
+      <c r="A539" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B539" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/112/dispensa-de-licitacao-n-0072020</t>
+        </is>
+      </c>
+      <c r="C539" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D539" t="n">
+        <v>404</v>
+      </c>
+      <c r="E539" t="n">
+        <v>3</v>
+      </c>
+      <c r="F539" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:07:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="540">
+      <c r="A540" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B540" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/112/dispensa-de-licitacao-n-0072020</t>
+        </is>
+      </c>
+      <c r="C540" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D540" t="n">
+        <v>0</v>
+      </c>
+      <c r="E540" t="n">
+        <v>3</v>
+      </c>
+      <c r="F540" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:08:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="541">
+      <c r="A541" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B541" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/111/dispensa-de-licitacao-n-0062020</t>
+        </is>
+      </c>
+      <c r="C541" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D541" t="n">
+        <v>404</v>
+      </c>
+      <c r="E541" t="n">
+        <v>3</v>
+      </c>
+      <c r="F541" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:08:35</t>
+        </is>
+      </c>
+    </row>
+    <row r="542">
+      <c r="A542" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B542" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/111/dispensa-de-licitacao-n-0062020</t>
+        </is>
+      </c>
+      <c r="C542" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D542" t="n">
+        <v>0</v>
+      </c>
+      <c r="E542" t="n">
+        <v>3</v>
+      </c>
+      <c r="F542" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:09:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="543">
+      <c r="A543" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B543" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/84/dispensa-de-licitacao-n-0042020</t>
+        </is>
+      </c>
+      <c r="C543" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D543" t="n">
+        <v>404</v>
+      </c>
+      <c r="E543" t="n">
+        <v>3</v>
+      </c>
+      <c r="F543" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:09:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="544">
+      <c r="A544" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B544" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/84/dispensa-de-licitacao-n-0042020</t>
+        </is>
+      </c>
+      <c r="C544" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D544" t="n">
+        <v>0</v>
+      </c>
+      <c r="E544" t="n">
+        <v>3</v>
+      </c>
+      <c r="F544" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:10:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="545">
+      <c r="A545" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B545" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/109/dispensa-de-licitacao-n-0042020-2</t>
+        </is>
+      </c>
+      <c r="C545" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D545" t="n">
+        <v>404</v>
+      </c>
+      <c r="E545" t="n">
+        <v>3</v>
+      </c>
+      <c r="F545" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:10:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="546">
+      <c r="A546" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B546" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/109/dispensa-de-licitacao-n-0042020-2</t>
+        </is>
+      </c>
+      <c r="C546" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D546" t="n">
+        <v>0</v>
+      </c>
+      <c r="E546" t="n">
+        <v>3</v>
+      </c>
+      <c r="F546" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:12:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="547">
+      <c r="A547" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B547" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/83/dispensa-de-licitacao-n-0032020</t>
+        </is>
+      </c>
+      <c r="C547" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D547" t="n">
+        <v>404</v>
+      </c>
+      <c r="E547" t="n">
+        <v>3</v>
+      </c>
+      <c r="F547" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:12:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="548">
+      <c r="A548" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B548" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/83/dispensa-de-licitacao-n-0032020</t>
+        </is>
+      </c>
+      <c r="C548" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D548" t="n">
+        <v>0</v>
+      </c>
+      <c r="E548" t="n">
+        <v>3</v>
+      </c>
+      <c r="F548" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:13:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="549">
+      <c r="A549" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B549" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/110/dispensa-de-licitacao-n-0032020-2</t>
+        </is>
+      </c>
+      <c r="C549" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D549" t="n">
+        <v>404</v>
+      </c>
+      <c r="E549" t="n">
+        <v>3</v>
+      </c>
+      <c r="F549" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:13:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="550">
+      <c r="A550" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B550" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/110/dispensa-de-licitacao-n-0032020-2</t>
+        </is>
+      </c>
+      <c r="C550" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D550" t="n">
+        <v>0</v>
+      </c>
+      <c r="E550" t="n">
+        <v>3</v>
+      </c>
+      <c r="F550" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:14:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="551">
+      <c r="A551" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B551" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/107/dispensa-de-licitacao-n-0022020</t>
+        </is>
+      </c>
+      <c r="C551" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D551" t="n">
+        <v>404</v>
+      </c>
+      <c r="E551" t="n">
+        <v>3</v>
+      </c>
+      <c r="F551" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:14:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="552">
+      <c r="A552" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B552" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/107/dispensa-de-licitacao-n-0022020</t>
+        </is>
+      </c>
+      <c r="C552" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D552" t="n">
+        <v>0</v>
+      </c>
+      <c r="E552" t="n">
+        <v>3</v>
+      </c>
+      <c r="F552" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:15:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="553">
+      <c r="A553" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B553" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/106/dispensa-de-licitacao-n-0012020</t>
+        </is>
+      </c>
+      <c r="C553" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D553" t="n">
+        <v>404</v>
+      </c>
+      <c r="E553" t="n">
+        <v>3</v>
+      </c>
+      <c r="F553" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:15:49</t>
+        </is>
+      </c>
+    </row>
+    <row r="554">
+      <c r="A554" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B554" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/106/dispensa-de-licitacao-n-0012020</t>
+        </is>
+      </c>
+      <c r="C554" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D554" t="n">
+        <v>0</v>
+      </c>
+      <c r="E554" t="n">
+        <v>3</v>
+      </c>
+      <c r="F554" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:16:59</t>
+        </is>
+      </c>
+    </row>
+    <row r="555">
+      <c r="A555" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B555" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/105/dispensa-de-licitacao-n-0092019</t>
+        </is>
+      </c>
+      <c r="C555" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D555" t="n">
+        <v>404</v>
+      </c>
+      <c r="E555" t="n">
+        <v>3</v>
+      </c>
+      <c r="F555" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:17:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="556">
+      <c r="A556" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B556" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/105/dispensa-de-licitacao-n-0092019</t>
+        </is>
+      </c>
+      <c r="C556" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D556" t="n">
+        <v>0</v>
+      </c>
+      <c r="E556" t="n">
+        <v>3</v>
+      </c>
+      <c r="F556" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:18:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="557">
+      <c r="A557" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B557" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/104/dispensa-de-licitacao-n-0082019</t>
+        </is>
+      </c>
+      <c r="C557" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D557" t="n">
+        <v>404</v>
+      </c>
+      <c r="E557" t="n">
+        <v>3</v>
+      </c>
+      <c r="F557" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:18:12</t>
+        </is>
+      </c>
+    </row>
+    <row r="558">
+      <c r="A558" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B558" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/104/dispensa-de-licitacao-n-0082019</t>
+        </is>
+      </c>
+      <c r="C558" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D558" t="n">
+        <v>0</v>
+      </c>
+      <c r="E558" t="n">
+        <v>3</v>
+      </c>
+      <c r="F558" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:19:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="559">
+      <c r="A559" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B559" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/101/dispensa-de-licitacao-n-0062019</t>
+        </is>
+      </c>
+      <c r="C559" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D559" t="n">
+        <v>404</v>
+      </c>
+      <c r="E559" t="n">
+        <v>3</v>
+      </c>
+      <c r="F559" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:19:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="560">
+      <c r="A560" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B560" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/101/dispensa-de-licitacao-n-0062019</t>
+        </is>
+      </c>
+      <c r="C560" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D560" t="n">
+        <v>0</v>
+      </c>
+      <c r="E560" t="n">
+        <v>3</v>
+      </c>
+      <c r="F560" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:20:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="561">
+      <c r="A561" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B561" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/100/dispensa-de-licitacao-n-0052019</t>
+        </is>
+      </c>
+      <c r="C561" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D561" t="n">
+        <v>404</v>
+      </c>
+      <c r="E561" t="n">
+        <v>3</v>
+      </c>
+      <c r="F561" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:20:36</t>
+        </is>
+      </c>
+    </row>
+    <row r="562">
+      <c r="A562" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B562" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/100/dispensa-de-licitacao-n-0052019</t>
+        </is>
+      </c>
+      <c r="C562" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D562" t="n">
+        <v>0</v>
+      </c>
+      <c r="E562" t="n">
+        <v>3</v>
+      </c>
+      <c r="F562" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:21:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B563" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/103/dispensa-de-licitacao-n-0042019</t>
+        </is>
+      </c>
+      <c r="C563" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D563" t="n">
+        <v>404</v>
+      </c>
+      <c r="E563" t="n">
+        <v>3</v>
+      </c>
+      <c r="F563" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:21:47</t>
+        </is>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B564" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/103/dispensa-de-licitacao-n-0042019</t>
+        </is>
+      </c>
+      <c r="C564" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D564" t="n">
+        <v>0</v>
+      </c>
+      <c r="E564" t="n">
+        <v>3</v>
+      </c>
+      <c r="F564" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:22:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B565" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/102/dispensa-de-licitacao-n-0032019</t>
+        </is>
+      </c>
+      <c r="C565" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D565" t="n">
+        <v>404</v>
+      </c>
+      <c r="E565" t="n">
+        <v>3</v>
+      </c>
+      <c r="F565" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:22:58</t>
+        </is>
+      </c>
+    </row>
+    <row r="566">
+      <c r="A566" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B566" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/102/dispensa-de-licitacao-n-0032019</t>
+        </is>
+      </c>
+      <c r="C566" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D566" t="n">
+        <v>0</v>
+      </c>
+      <c r="E566" t="n">
+        <v>3</v>
+      </c>
+      <c r="F566" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:24:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="567">
+      <c r="A567" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B567" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/99/dispensa-de-licitacao-n-0022019</t>
+        </is>
+      </c>
+      <c r="C567" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D567" t="n">
+        <v>404</v>
+      </c>
+      <c r="E567" t="n">
+        <v>3</v>
+      </c>
+      <c r="F567" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:24:10</t>
+        </is>
+      </c>
+    </row>
+    <row r="568">
+      <c r="A568" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B568" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/99/dispensa-de-licitacao-n-0022019</t>
+        </is>
+      </c>
+      <c r="C568" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D568" t="n">
+        <v>0</v>
+      </c>
+      <c r="E568" t="n">
+        <v>3</v>
+      </c>
+      <c r="F568" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:25:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="569">
+      <c r="A569" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B569" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/98/dispensa-de-licitacao-n-0012019</t>
+        </is>
+      </c>
+      <c r="C569" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D569" t="n">
+        <v>404</v>
+      </c>
+      <c r="E569" t="n">
+        <v>3</v>
+      </c>
+      <c r="F569" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:25:22</t>
+        </is>
+      </c>
+    </row>
+    <row r="570">
+      <c r="A570" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B570" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/98/dispensa-de-licitacao-n-0012019</t>
+        </is>
+      </c>
+      <c r="C570" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D570" t="n">
+        <v>0</v>
+      </c>
+      <c r="E570" t="n">
+        <v>3</v>
+      </c>
+      <c r="F570" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:26:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="571">
+      <c r="A571" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B571" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/97/dispensa-de-licitacao-n-0122018</t>
+        </is>
+      </c>
+      <c r="C571" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D571" t="n">
+        <v>404</v>
+      </c>
+      <c r="E571" t="n">
+        <v>3</v>
+      </c>
+      <c r="F571" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:26:34</t>
+        </is>
+      </c>
+    </row>
+    <row r="572">
+      <c r="A572" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B572" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/97/dispensa-de-licitacao-n-0122018</t>
+        </is>
+      </c>
+      <c r="C572" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D572" t="n">
+        <v>0</v>
+      </c>
+      <c r="E572" t="n">
+        <v>3</v>
+      </c>
+      <c r="F572" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:27:44</t>
+        </is>
+      </c>
+    </row>
+    <row r="573">
+      <c r="A573" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B573" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/96/dispensa-de-licitacao-n-0112018</t>
+        </is>
+      </c>
+      <c r="C573" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D573" t="n">
+        <v>404</v>
+      </c>
+      <c r="E573" t="n">
+        <v>3</v>
+      </c>
+      <c r="F573" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:27:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="574">
+      <c r="A574" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B574" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/96/dispensa-de-licitacao-n-0112018</t>
+        </is>
+      </c>
+      <c r="C574" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D574" t="n">
+        <v>0</v>
+      </c>
+      <c r="E574" t="n">
+        <v>3</v>
+      </c>
+      <c r="F574" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:28:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="575">
+      <c r="A575" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B575" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/95/dispensa-de-licitacao-n-0102018</t>
+        </is>
+      </c>
+      <c r="C575" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D575" t="n">
+        <v>404</v>
+      </c>
+      <c r="E575" t="n">
+        <v>3</v>
+      </c>
+      <c r="F575" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:28:57</t>
+        </is>
+      </c>
+    </row>
+    <row r="576">
+      <c r="A576" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B576" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/95/dispensa-de-licitacao-n-0102018</t>
+        </is>
+      </c>
+      <c r="C576" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D576" t="n">
+        <v>0</v>
+      </c>
+      <c r="E576" t="n">
+        <v>3</v>
+      </c>
+      <c r="F576" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:30:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="577">
+      <c r="A577" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B577" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/94/dispensa-de-licitacao-n-0092018</t>
+        </is>
+      </c>
+      <c r="C577" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D577" t="n">
+        <v>404</v>
+      </c>
+      <c r="E577" t="n">
+        <v>3</v>
+      </c>
+      <c r="F577" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:30:08</t>
+        </is>
+      </c>
+    </row>
+    <row r="578">
+      <c r="A578" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B578" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/94/dispensa-de-licitacao-n-0092018</t>
+        </is>
+      </c>
+      <c r="C578" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D578" t="n">
+        <v>0</v>
+      </c>
+      <c r="E578" t="n">
+        <v>3</v>
+      </c>
+      <c r="F578" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:31:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="579">
+      <c r="A579" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B579" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/93/dispensa-de-licitacao-n-0082018</t>
+        </is>
+      </c>
+      <c r="C579" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D579" t="n">
+        <v>404</v>
+      </c>
+      <c r="E579" t="n">
+        <v>3</v>
+      </c>
+      <c r="F579" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:31:20</t>
+        </is>
+      </c>
+    </row>
+    <row r="580">
+      <c r="A580" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B580" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/93/dispensa-de-licitacao-n-0082018</t>
+        </is>
+      </c>
+      <c r="C580" t="inlineStr">
+        <is>
+          <t>SELENIUM_ERRO: InvalidSessionIdException</t>
+        </is>
+      </c>
+      <c r="D580" t="n">
+        <v>0</v>
+      </c>
+      <c r="E580" t="n">
+        <v>3</v>
+      </c>
+      <c r="F580" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:47:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="581">
+      <c r="A581" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B581" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/92/dispensa-de-licitacao-n-0072018</t>
+        </is>
+      </c>
+      <c r="C581" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D581" t="n">
+        <v>404</v>
+      </c>
+      <c r="E581" t="n">
+        <v>3</v>
+      </c>
+      <c r="F581" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:47:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="582">
+      <c r="A582" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B582" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/92/dispensa-de-licitacao-n-0072018</t>
+        </is>
+      </c>
+      <c r="C582" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D582" t="n">
+        <v>0</v>
+      </c>
+      <c r="E582" t="n">
+        <v>3</v>
+      </c>
+      <c r="F582" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:56:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="583">
+      <c r="A583" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B583" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/91/dispensa-de-licitacao-n-0062018</t>
+        </is>
+      </c>
+      <c r="C583" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D583" t="n">
+        <v>404</v>
+      </c>
+      <c r="E583" t="n">
+        <v>3</v>
+      </c>
+      <c r="F583" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:56:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="584">
+      <c r="A584" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B584" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/91/dispensa-de-licitacao-n-0062018</t>
+        </is>
+      </c>
+      <c r="C584" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D584" t="n">
+        <v>0</v>
+      </c>
+      <c r="E584" t="n">
+        <v>3</v>
+      </c>
+      <c r="F584" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:57:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="585">
+      <c r="A585" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B585" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/90/dispensa-de-licitacao-n-0052018</t>
+        </is>
+      </c>
+      <c r="C585" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D585" t="n">
+        <v>404</v>
+      </c>
+      <c r="E585" t="n">
+        <v>3</v>
+      </c>
+      <c r="F585" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:57:42</t>
+        </is>
+      </c>
+    </row>
+    <row r="586">
+      <c r="A586" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B586" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/90/dispensa-de-licitacao-n-0052018</t>
+        </is>
+      </c>
+      <c r="C586" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D586" t="n">
+        <v>0</v>
+      </c>
+      <c r="E586" t="n">
+        <v>3</v>
+      </c>
+      <c r="F586" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:58:53</t>
+        </is>
+      </c>
+    </row>
+    <row r="587">
+      <c r="A587" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B587" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/89/dispensa-de-licitacao-n-0042018</t>
+        </is>
+      </c>
+      <c r="C587" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D587" t="n">
+        <v>404</v>
+      </c>
+      <c r="E587" t="n">
+        <v>3</v>
+      </c>
+      <c r="F587" t="inlineStr">
+        <is>
+          <t>2026-07-31 21:58:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="588">
+      <c r="A588" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B588" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/89/dispensa-de-licitacao-n-0042018</t>
+        </is>
+      </c>
+      <c r="C588" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D588" t="n">
+        <v>0</v>
+      </c>
+      <c r="E588" t="n">
+        <v>3</v>
+      </c>
+      <c r="F588" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:00:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="589">
+      <c r="A589" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B589" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/87/dispensa-de-licitacao-n-0032018</t>
+        </is>
+      </c>
+      <c r="C589" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D589" t="n">
+        <v>404</v>
+      </c>
+      <c r="E589" t="n">
+        <v>3</v>
+      </c>
+      <c r="F589" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:00:06</t>
+        </is>
+      </c>
+    </row>
+    <row r="590">
+      <c r="A590" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B590" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/87/dispensa-de-licitacao-n-0032018</t>
+        </is>
+      </c>
+      <c r="C590" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D590" t="n">
+        <v>0</v>
+      </c>
+      <c r="E590" t="n">
+        <v>3</v>
+      </c>
+      <c r="F590" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:01:16</t>
+        </is>
+      </c>
+    </row>
+    <row r="591">
+      <c r="A591" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B591" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/88/dispensa-de-licitacao-n-0022018</t>
+        </is>
+      </c>
+      <c r="C591" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D591" t="n">
+        <v>404</v>
+      </c>
+      <c r="E591" t="n">
+        <v>3</v>
+      </c>
+      <c r="F591" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:01:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="592">
+      <c r="A592" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B592" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/88/dispensa-de-licitacao-n-0022018</t>
+        </is>
+      </c>
+      <c r="C592" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D592" t="n">
+        <v>0</v>
+      </c>
+      <c r="E592" t="n">
+        <v>3</v>
+      </c>
+      <c r="F592" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:02:31</t>
+        </is>
+      </c>
+    </row>
+    <row r="593">
+      <c r="A593" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B593" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/86/dispensa-de-licitacao-n-0012018</t>
+        </is>
+      </c>
+      <c r="C593" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D593" t="n">
+        <v>404</v>
+      </c>
+      <c r="E593" t="n">
+        <v>3</v>
+      </c>
+      <c r="F593" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:02:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="594">
+      <c r="A594" t="inlineStr">
+        <is>
+          <t>xambre</t>
+        </is>
+      </c>
+      <c r="B594" t="inlineStr">
+        <is>
+          <t>https://www.xambre.pr.gov.br/model/view/86/dispensa-de-licitacao-n-0012018</t>
+        </is>
+      </c>
+      <c r="C594" t="inlineStr">
+        <is>
+          <t>CAPTCHA_NAO_RESOLVIDO</t>
+        </is>
+      </c>
+      <c r="D594" t="n">
+        <v>0</v>
+      </c>
+      <c r="E594" t="n">
+        <v>3</v>
+      </c>
+      <c r="F594" t="inlineStr">
+        <is>
+          <t>2026-07-31 22:03:43</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
